--- a/assessment_schedule.xlsx
+++ b/assessment_schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hudson Lynam\Documents\websites\csc110-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFCA0712-4969-4B8E-A7B8-9720D7F647F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D347A6C-C7E0-4B55-8D76-30177E15B79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="60">
   <si>
     <t>number</t>
   </si>
@@ -204,9 +204,6 @@
     <t>Quiz 11</t>
   </si>
   <si>
-    <t>Short Programming Project 12</t>
-  </si>
-  <si>
     <t>Programming Project 12</t>
   </si>
   <si>
@@ -219,10 +216,10 @@
     <t>Quiz 12</t>
   </si>
   <si>
-    <t>6pm-8pm</t>
-  </si>
-  <si>
     <t>Programming Project 13</t>
+  </si>
+  <si>
+    <t>3:30pm-5:30pm</t>
   </si>
 </sst>
 </file>
@@ -598,7 +595,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="2">
-        <v>46038</v>
+        <v>46260</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>5</v>
@@ -612,7 +609,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="2">
-        <v>46043</v>
+        <v>46267</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>5</v>
@@ -629,7 +626,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="2">
-        <v>46045</v>
+        <v>46269</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>6</v>
@@ -644,7 +641,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="2">
-        <v>46050</v>
+        <v>46274</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>5</v>
@@ -659,7 +656,7 @@
         <v>9</v>
       </c>
       <c r="C6" s="2">
-        <v>46050</v>
+        <v>46274</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>6</v>
@@ -673,7 +670,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="2">
-        <v>46050</v>
+        <v>46276</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>6</v>
@@ -687,7 +684,7 @@
         <v>12</v>
       </c>
       <c r="C8" s="2">
-        <v>46052</v>
+        <v>46276</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>6</v>
@@ -701,7 +698,7 @@
         <v>15</v>
       </c>
       <c r="C9" s="2">
-        <v>46057</v>
+        <v>46281</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>5</v>
@@ -718,7 +715,7 @@
         <v>13</v>
       </c>
       <c r="C10" s="2">
-        <v>46057</v>
+        <v>46281</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>6</v>
@@ -732,7 +729,7 @@
         <v>14</v>
       </c>
       <c r="C11" s="2">
-        <v>46057</v>
+        <v>46283</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>6</v>
@@ -746,7 +743,7 @@
         <v>16</v>
       </c>
       <c r="C12" s="2">
-        <v>46059</v>
+        <v>46283</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>6</v>
@@ -760,7 +757,7 @@
         <v>19</v>
       </c>
       <c r="C13" s="2">
-        <v>46064</v>
+        <v>46288</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>5</v>
@@ -777,7 +774,7 @@
         <v>17</v>
       </c>
       <c r="C14" s="2">
-        <v>46064</v>
+        <v>46288</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>6</v>
@@ -791,7 +788,7 @@
         <v>18</v>
       </c>
       <c r="C15" s="2">
-        <v>46064</v>
+        <v>46290</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>6</v>
@@ -805,7 +802,7 @@
         <v>20</v>
       </c>
       <c r="C16" s="2">
-        <v>46066</v>
+        <v>46290</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>6</v>
@@ -819,7 +816,7 @@
         <v>27</v>
       </c>
       <c r="C17" s="2">
-        <v>46071</v>
+        <v>46295</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>5</v>
@@ -836,7 +833,7 @@
         <v>22</v>
       </c>
       <c r="C18" s="2">
-        <v>46071</v>
+        <v>46295</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>6</v>
@@ -850,7 +847,7 @@
         <v>23</v>
       </c>
       <c r="C19" s="2">
-        <v>46071</v>
+        <v>46297</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>6</v>
@@ -864,7 +861,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="2">
-        <v>46073</v>
+        <v>46297</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>6</v>
@@ -878,7 +875,7 @@
         <v>21</v>
       </c>
       <c r="C21" s="2">
-        <v>46078</v>
+        <v>46302</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>5</v>
@@ -892,7 +889,7 @@
         <v>25</v>
       </c>
       <c r="C22" s="2">
-        <v>46080</v>
+        <v>46302</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>6</v>
@@ -906,7 +903,7 @@
         <v>26</v>
       </c>
       <c r="C23" s="2">
-        <v>46080</v>
+        <v>46304</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>6</v>
@@ -920,7 +917,7 @@
         <v>28</v>
       </c>
       <c r="C24" s="2">
-        <v>46083</v>
+        <v>46304</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>6</v>
@@ -934,7 +931,7 @@
         <v>50</v>
       </c>
       <c r="C25" s="2">
-        <v>46085</v>
+        <v>46309</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>5</v>
@@ -951,7 +948,7 @@
         <v>29</v>
       </c>
       <c r="C26" s="2">
-        <v>46085</v>
+        <v>46309</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>6</v>
@@ -965,7 +962,7 @@
         <v>30</v>
       </c>
       <c r="C27" s="2">
-        <v>46085</v>
+        <v>46311</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>6</v>
@@ -979,7 +976,7 @@
         <v>31</v>
       </c>
       <c r="C28" s="2">
-        <v>46087</v>
+        <v>46311</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>6</v>
@@ -993,7 +990,7 @@
         <v>51</v>
       </c>
       <c r="C29" s="2">
-        <v>46099</v>
+        <v>46316</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>5</v>
@@ -1007,7 +1004,7 @@
         <v>32</v>
       </c>
       <c r="C30" s="2">
-        <v>46099</v>
+        <v>46316</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>6</v>
@@ -1021,7 +1018,7 @@
         <v>33</v>
       </c>
       <c r="C31" s="2">
-        <v>46099</v>
+        <v>46318</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>6</v>
@@ -1035,7 +1032,7 @@
         <v>34</v>
       </c>
       <c r="C32" s="2">
-        <v>46101</v>
+        <v>46318</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>6</v>
@@ -1046,10 +1043,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C33" s="2">
-        <v>46106</v>
+        <v>46323</v>
       </c>
       <c r="D33" s="11" t="s">
         <v>5</v>
@@ -1063,7 +1060,7 @@
         <v>36</v>
       </c>
       <c r="C34" s="2">
-        <v>46106</v>
+        <v>46323</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>6</v>
@@ -1077,7 +1074,7 @@
         <v>35</v>
       </c>
       <c r="C35" s="2">
-        <v>46113</v>
+        <v>46330</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>5</v>
@@ -1091,7 +1088,7 @@
         <v>37</v>
       </c>
       <c r="C36" s="2">
-        <v>46113</v>
+        <v>46330</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>6</v>
@@ -1105,7 +1102,7 @@
         <v>38</v>
       </c>
       <c r="C37" s="2">
-        <v>46113</v>
+        <v>46332</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>6</v>
@@ -1119,7 +1116,7 @@
         <v>39</v>
       </c>
       <c r="C38" s="2">
-        <v>46115</v>
+        <v>46332</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>6</v>
@@ -1133,7 +1130,7 @@
         <v>40</v>
       </c>
       <c r="C39" s="2">
-        <v>46120</v>
+        <v>46337</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>6</v>
@@ -1147,7 +1144,7 @@
         <v>41</v>
       </c>
       <c r="C40" s="2">
-        <v>46120</v>
+        <v>46339</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>6</v>
@@ -1161,7 +1158,7 @@
         <v>42</v>
       </c>
       <c r="C41" s="2">
-        <v>46122</v>
+        <v>46339</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>6</v>
@@ -1175,7 +1172,7 @@
         <v>52</v>
       </c>
       <c r="C42" s="2">
-        <v>46127</v>
+        <v>46344</v>
       </c>
       <c r="D42" s="12" t="s">
         <v>5</v>
@@ -1189,7 +1186,7 @@
         <v>43</v>
       </c>
       <c r="C43" s="2">
-        <v>46127</v>
+        <v>46344</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>6</v>
@@ -1204,7 +1201,7 @@
         <v>44</v>
       </c>
       <c r="C44" s="2">
-        <v>46127</v>
+        <v>46346</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>6</v>
@@ -1218,7 +1215,7 @@
         <v>45</v>
       </c>
       <c r="C45" s="2">
-        <v>46129</v>
+        <v>46346</v>
       </c>
       <c r="D45" s="12" t="s">
         <v>6</v>
@@ -1232,7 +1229,7 @@
         <v>53</v>
       </c>
       <c r="C46" s="2">
-        <v>46134</v>
+        <v>46358</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>5</v>
@@ -1246,7 +1243,7 @@
         <v>46</v>
       </c>
       <c r="C47" s="2">
-        <v>46134</v>
+        <v>46358</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>6</v>
@@ -1260,7 +1257,7 @@
         <v>48</v>
       </c>
       <c r="C48" s="2">
-        <v>46134</v>
+        <v>46360</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>6</v>
@@ -1274,7 +1271,7 @@
         <v>49</v>
       </c>
       <c r="C49" s="2">
-        <v>46139</v>
+        <v>46360</v>
       </c>
       <c r="D49" s="12" t="s">
         <v>6</v>
@@ -1285,10 +1282,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C50" s="2">
-        <v>46141</v>
+        <v>46365</v>
       </c>
       <c r="D50" s="12" t="s">
         <v>5</v>
@@ -1302,7 +1299,7 @@
         <v>47</v>
       </c>
       <c r="C51" s="2">
-        <v>46143</v>
+        <v>46365</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>6</v>
@@ -1311,14 +1308,14 @@
       <c r="F51" s="9"/>
     </row>
     <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="1">
+      <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>54</v>
       </c>
       <c r="C52" s="2">
-        <v>46143</v>
+        <v>46365</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>6</v>
@@ -1328,11 +1325,11 @@
       <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" s="11" t="s">
-        <v>55</v>
+      <c r="B53" s="14" t="s">
+        <v>58</v>
       </c>
       <c r="C53" s="2">
-        <v>46146</v>
+        <v>46365</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>6</v>
@@ -1342,30 +1339,17 @@
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" s="14" t="s">
-        <v>60</v>
+      <c r="B54" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="C54" s="2">
-        <v>46146</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C55" s="2">
-        <v>46150</v>
-      </c>
-      <c r="D55" s="14" t="s">
+        <v>46367</v>
+      </c>
+      <c r="D54" s="14" t="s">
         <v>59</v>
       </c>
     </row>
+    <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
       <c r="C56" s="2"/>

--- a/assessment_schedule.xlsx
+++ b/assessment_schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hudson Lynam\Documents\websites\csc110-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D347A6C-C7E0-4B55-8D76-30177E15B79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6958FA9B-8A2B-4AB1-9A60-B847E2F7C1FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="61">
   <si>
     <t>number</t>
   </si>
@@ -220,6 +220,9 @@
   </si>
   <si>
     <t>3:30pm-5:30pm</t>
+  </si>
+  <si>
+    <t>Short Programming Project 12</t>
   </si>
 </sst>
 </file>
@@ -637,29 +640,29 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2">
+        <v>46269</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>11</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46274</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="7"/>
-    </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="C6" s="2">
         <v>46274</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>6</v>
+      <c r="D6" s="12" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -667,10 +670,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" s="2">
-        <v>46276</v>
+        <v>46274</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>6</v>
@@ -681,7 +684,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C8" s="2">
         <v>46276</v>
@@ -694,14 +697,14 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>15</v>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C9" s="2">
-        <v>46281</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>5</v>
+        <v>46276</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="2"/>
@@ -711,25 +714,25 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>13</v>
+      <c r="B10" s="14" t="s">
+        <v>15</v>
       </c>
       <c r="C10" s="2">
         <v>46281</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>6</v>
+      <c r="D10" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="1">
+      <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11" s="2">
-        <v>46283</v>
+        <v>46281</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>6</v>
@@ -739,8 +742,8 @@
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>16</v>
+      <c r="B12" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="C12" s="2">
         <v>46283</v>
@@ -753,14 +756,14 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="14" t="s">
-        <v>19</v>
+      <c r="B13" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="C13" s="2">
-        <v>46288</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>5</v>
+        <v>46283</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="2"/>
@@ -770,14 +773,14 @@
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>17</v>
+      <c r="B14" s="14" t="s">
+        <v>19</v>
       </c>
       <c r="C14" s="2">
         <v>46288</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>6</v>
+      <c r="D14" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -785,21 +788,21 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" s="2">
-        <v>46290</v>
+        <v>46288</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="1">
+      <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C16" s="2">
         <v>46290</v>
@@ -812,14 +815,14 @@
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="14" t="s">
-        <v>27</v>
+      <c r="B17" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="C17" s="2">
-        <v>46295</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>5</v>
+        <v>46290</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>6</v>
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="2"/>
@@ -829,14 +832,14 @@
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>22</v>
+      <c r="B18" s="14" t="s">
+        <v>27</v>
       </c>
       <c r="C18" s="2">
         <v>46295</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>6</v>
+      <c r="D18" s="5" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -844,10 +847,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" s="2">
-        <v>46297</v>
+        <v>46295</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>6</v>
@@ -857,8 +860,8 @@
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>24</v>
+      <c r="B20" s="14" t="s">
+        <v>26</v>
       </c>
       <c r="C20" s="2">
         <v>46297</v>
@@ -868,31 +871,31 @@
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="1">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="11" t="s">
-        <v>21</v>
+      <c r="B21" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="C21" s="2">
-        <v>46302</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>5</v>
+        <v>46297</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>25</v>
+      <c r="B22" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="C22" s="2">
         <v>46302</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>6</v>
+      <c r="D22" s="12" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -900,10 +903,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23" s="2">
-        <v>46304</v>
+        <v>46302</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>6</v>
@@ -913,8 +916,8 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>28</v>
+      <c r="B24" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C24" s="2">
         <v>46304</v>
@@ -927,42 +930,42 @@
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="14" t="s">
-        <v>50</v>
+      <c r="B25" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="C25" s="2">
-        <v>46309</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>5</v>
+        <v>46304</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="E25" s="7"/>
       <c r="F25" s="2"/>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="1">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>29</v>
+      <c r="B26" s="14" t="s">
+        <v>50</v>
       </c>
       <c r="C26" s="2">
         <v>46309</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>6</v>
+      <c r="D26" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>30</v>
+      <c r="B27" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="C27" s="2">
-        <v>46311</v>
+        <v>46309</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>6</v>
@@ -972,8 +975,8 @@
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>31</v>
+      <c r="B28" s="14" t="s">
+        <v>33</v>
       </c>
       <c r="C28" s="2">
         <v>46311</v>
@@ -986,39 +989,39 @@
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="14" t="s">
-        <v>51</v>
+      <c r="B29" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="C29" s="2">
-        <v>46316</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>5</v>
+        <v>46311</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>32</v>
+      <c r="B30" s="14" t="s">
+        <v>51</v>
       </c>
       <c r="C30" s="2">
         <v>46316</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>6</v>
+      <c r="D30" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="1">
+      <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C31" s="2">
-        <v>46318</v>
+        <v>46316</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>6</v>
@@ -1028,8 +1031,8 @@
       <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>34</v>
+      <c r="B32" s="14" t="s">
+        <v>38</v>
       </c>
       <c r="C32" s="2">
         <v>46318</v>
@@ -1042,56 +1045,56 @@
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="14" t="s">
-        <v>56</v>
+      <c r="B33" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="C33" s="2">
-        <v>46323</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>5</v>
+        <v>46318</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>36</v>
+      <c r="B34" s="14" t="s">
+        <v>56</v>
       </c>
       <c r="C34" s="2">
         <v>46323</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>6</v>
+      <c r="D34" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" s="2">
+        <v>46323</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36">
         <v>35</v>
       </c>
-      <c r="C35" s="2">
-        <v>46330</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="1">
+      <c r="B36" s="11" t="s">
         <v>35</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="C36" s="2">
         <v>46330</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>6</v>
+      <c r="D36" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1099,10 +1102,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C37" s="2">
-        <v>46332</v>
+        <v>46330</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>6</v>
@@ -1112,8 +1115,8 @@
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>39</v>
+      <c r="B38" s="14" t="s">
+        <v>41</v>
       </c>
       <c r="C38" s="2">
         <v>46332</v>
@@ -1126,11 +1129,11 @@
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>40</v>
+      <c r="B39" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="C39" s="2">
-        <v>46337</v>
+        <v>46332</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>6</v>
@@ -1141,21 +1144,21 @@
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C40" s="2">
-        <v>46339</v>
+        <v>46337</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="1">
+      <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" s="4" t="s">
-        <v>42</v>
+      <c r="B41" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="C41" s="2">
         <v>46339</v>
@@ -1168,28 +1171,28 @@
       <c r="A42" s="1">
         <v>41</v>
       </c>
-      <c r="B42" s="14" t="s">
-        <v>52</v>
+      <c r="B42" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="C42" s="2">
-        <v>46344</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>5</v>
+        <v>46339</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>43</v>
+      <c r="B43" s="14" t="s">
+        <v>52</v>
       </c>
       <c r="C43" s="2">
         <v>46344</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>6</v>
+      <c r="D43" s="12" t="s">
+        <v>5</v>
       </c>
       <c r="H43" s="10"/>
     </row>
@@ -1197,11 +1200,11 @@
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" s="4" t="s">
-        <v>44</v>
+      <c r="B44" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="C44" s="2">
-        <v>46346</v>
+        <v>46344</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>6</v>
@@ -1211,42 +1214,42 @@
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" s="13" t="s">
-        <v>45</v>
+      <c r="B45" s="14" t="s">
+        <v>48</v>
       </c>
       <c r="C45" s="2">
         <v>46346</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="D45" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="1">
+      <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" s="14" t="s">
-        <v>53</v>
+      <c r="B46" s="13" t="s">
+        <v>45</v>
       </c>
       <c r="C46" s="2">
-        <v>46358</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>5</v>
+        <v>46346</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>46</v>
       </c>
-      <c r="B47" s="4" t="s">
-        <v>46</v>
+      <c r="B47" s="14" t="s">
+        <v>53</v>
       </c>
       <c r="C47" s="2">
         <v>46358</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>6</v>
+      <c r="D47" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1254,10 +1257,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C48" s="2">
-        <v>46360</v>
+        <v>46358</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>6</v>
@@ -1267,13 +1270,13 @@
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" s="11" t="s">
-        <v>49</v>
+      <c r="B49" s="14" t="s">
+        <v>60</v>
       </c>
       <c r="C49" s="2">
         <v>46360</v>
       </c>
-      <c r="D49" s="12" t="s">
+      <c r="D49" s="3" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1281,38 +1284,38 @@
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" s="14" t="s">
+      <c r="B50" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C50" s="2">
+        <v>46360</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" s="14" t="s">
         <v>57</v>
-      </c>
-      <c r="C50" s="2">
-        <v>46365</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="1">
-        <v>50</v>
-      </c>
-      <c r="B51" s="8" t="s">
-        <v>47</v>
       </c>
       <c r="C51" s="2">
         <v>46365</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>6</v>
+      <c r="D51" s="12" t="s">
+        <v>5</v>
       </c>
       <c r="E51" s="9"/>
       <c r="F51" s="9"/>
     </row>
     <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52">
+      <c r="A52" s="1">
         <v>51</v>
       </c>
-      <c r="B52" s="11" t="s">
-        <v>54</v>
+      <c r="B52" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="C52" s="2">
         <v>46365</v>
@@ -1325,8 +1328,8 @@
       <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" s="14" t="s">
-        <v>58</v>
+      <c r="B53" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="C53" s="2">
         <v>46365</v>
@@ -1339,17 +1342,30 @@
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" s="11" t="s">
+      <c r="B54" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C54" s="2">
+        <v>46365</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C54" s="2">
+      <c r="C55" s="2">
         <v>46367</v>
       </c>
-      <c r="D54" s="14" t="s">
+      <c r="D55" s="14" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
       <c r="C56" s="2"/>
